--- a/instore_sales.xlsx
+++ b/instore_sales.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="68" documentId="8_{AF2EB71F-99AB-4A56-A83D-45B9C7330250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F3B7011-272E-424A-99A9-44F7E640B000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{27BF2078-A1DF-476C-8F8B-934B9EFFC071}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{27BF2078-A1DF-476C-8F8B-934B9EFFC071}"/>
   </bookViews>
   <sheets>
     <sheet name="instore_sales" sheetId="1" r:id="rId1"/>
@@ -3730,10 +3730,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
